--- a/exports/orders.xlsx
+++ b/exports/orders.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>11 Oct 2026, 11:07 PM</t>
+          <t>12 Oct 2026, 12:09 AM</t>
         </is>
       </c>
     </row>

--- a/exports/orders.xlsx
+++ b/exports/orders.xlsx
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>12 Oct 2026, 12:09 AM</t>
+          <t>12 Oct 2026, 12:18 AM</t>
         </is>
       </c>
     </row>
